--- a/Result/profitability/1527.xlsx
+++ b/Result/profitability/1527.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-2.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12625</v>
+        <v>0.08375000000000005</v>
       </c>
       <c r="N2" t="n">
-        <v>22.62125</v>
+        <v>20.79375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.71</v>
       </c>
       <c r="M3" t="n">
-        <v>0.10875</v>
+        <v>0.13125</v>
       </c>
       <c r="N3" t="n">
-        <v>22.0375</v>
+        <v>20.8175</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1925</v>
+        <v>0.14</v>
       </c>
       <c r="N4" t="n">
-        <v>22.345</v>
+        <v>20.90625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.85</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1825</v>
+        <v>0.3325</v>
       </c>
       <c r="N5" t="n">
-        <v>22.90875</v>
+        <v>21.85125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.96</v>
       </c>
       <c r="M6" t="n">
-        <v>0.38875</v>
+        <v>0.3525</v>
       </c>
       <c r="N6" t="n">
-        <v>23.48625</v>
+        <v>22.86</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>0.23125</v>
+        <v>0.235</v>
       </c>
       <c r="N7" t="n">
-        <v>23.9625</v>
+        <v>23.46</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0.21125</v>
+        <v>0.235</v>
       </c>
       <c r="N8" t="n">
-        <v>25.43875</v>
+        <v>24.81375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.98</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5349999999999999</v>
+        <v>0.535</v>
       </c>
       <c r="N11" t="n">
         <v>27.44</v>
@@ -1899,7 +1899,7 @@
         <v>-0.11</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3962499999999999</v>
+        <v>0.39625</v>
       </c>
       <c r="N12" t="n">
         <v>27.89125</v>
@@ -2026,7 +2026,7 @@
         <v>-1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1199999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="N13" t="n">
         <v>27.68</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>703</v>
+      </c>
+      <c r="D75" t="n">
+        <v>609</v>
+      </c>
+      <c r="E75" t="n">
+        <v>94</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>91</v>
+      </c>
+      <c r="J75" t="n">
+        <v>87</v>
+      </c>
+      <c r="K75" t="n">
+        <v>70</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.7075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.271591526344378</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.739130434782609</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3868312757201646</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
